--- a/Capstone_1/worrobah_territory_chart.xlsx
+++ b/Capstone_1/worrobah_territory_chart.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jordan's River\Documents\DataAnalytics\Capstone_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorda\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AE87FD6A-1C8F-42E0-9E41-9AC15FACCCB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1976606-915D-45D9-912F-06710FB46202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{54EF7CEE-DC1A-4451-8CBB-35067D5FAB33}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{54EF7CEE-DC1A-4451-8CBB-35067D5FAB33}"/>
   </bookViews>
   <sheets>
     <sheet name="Monthly Revenue" sheetId="4" r:id="rId1"/>
@@ -20,14 +20,14 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="11" r:id="rId5"/>
-    <pivotCache cacheId="19" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
+    <pivotCache cacheId="4" r:id="rId6"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="68">
   <si>
     <t>Month</t>
   </si>
@@ -222,9 +222,6 @@
   </si>
   <si>
     <t>Row Labels</t>
-  </si>
-  <si>
-    <t>(blank)</t>
   </si>
   <si>
     <t>Grand Total</t>
@@ -795,1127 +792,6 @@
       <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[worrobah_territory_chart.xlsx]Monthly Revenue!PivotTable4</c:name>
-    <c:fmtId val="0"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Monthly Revenue'!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Monthly Revenue'!$A$2:$A$51</c:f>
-              <c:strCache>
-                <c:ptCount val="49"/>
-                <c:pt idx="0">
-                  <c:v>2022-01</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2022-02</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2022-03</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2022-04</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2022-05</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2022-06</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2022-07</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2022-08</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2022-09</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2022-10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2022-11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2022-12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2023-01</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2023-02</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2023-03</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2023-04</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>2023-05</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2023-06</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>2023-07</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2023-08</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>2023-09</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>2023-10</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>2023-11</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>2023-12</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>2024-01</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>2024-02</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>2024-03</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>2024-04</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>2024-05</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>2024-06</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>2024-07</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>2024-08</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>2024-09</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>2024-10</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>2024-11</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>2024-12</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>2025-01</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>2025-02</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>2025-03</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>2025-04</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>2025-05</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2025-06</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>2025-07</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>2025-08</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>2025-09</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>2025-10</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>2025-11</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>2025-12</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>(blank)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Monthly Revenue'!$B$2:$B$51</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
-                <c:pt idx="0">
-                  <c:v>58635.53</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>60262.97</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>57143.4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>56880.02</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>51805.22</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>60549.86</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>56250.74</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>55052.53</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>60495.63</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>56896.98</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>58402.69</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>55006.46</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>85210.01</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>86906.65</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>79964.160000000003</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>97173.99</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>101370.73</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>83465.899999999994</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>90818.8</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>89422.22</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>89196.88</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>85095.72</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>79627.33</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>75904.66</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>94306.43</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>75083.7</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>99439.5</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>99105.22</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>87328.99</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>86955.71</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>89422.22</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>91189.41</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>83103.19</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>80543.34</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>74988.649999999994</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>85210.01</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>135193.89000000001</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>104990.83</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>119415.67999999999</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>117652.02</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>119352.07</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>135192.03</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>126976.23</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>133776.6</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>119597</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>185241.67</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>126941.06</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>128272.56</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A9D6-41D2-AFE7-0259E2C303A1}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="591950463"/>
-        <c:axId val="591950943"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="591950463"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="591950943"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="591950943"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="591950463"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[worrobah_territory_chart.xlsx]Total Revenue!PivotTable6</c:name>
-    <c:fmtId val="0"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Total Revenue'!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Total Revenue'!$A$2:$A$14</c:f>
-              <c:strCache>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>Albany</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Brooklyn</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Buffalo</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Elmira</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Ithaca</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>New York</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Oswego</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Plattsburgh</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Poestenkill</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Queens</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Rochester</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Syracuse</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Total Revenue'!$B$2:$B$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>310389.02</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>304732.76</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>314979.99</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>313971.65000000002</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>313920.05</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>621565.02</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>302862.71000000002</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>311520.52</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>334175.88</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>288553.14</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>607148.21</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>306998.14</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-813D-4B3C-911B-8B64EC8871EF}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:axId val="596524735"/>
-        <c:axId val="596523775"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="596524735"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="596523775"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="596523775"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="596524735"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:overlay val="0"/>
@@ -2462,6 +1338,1365 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="105"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="5"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[worrobah_territory_chart.xlsx]Monthly Revenue!PivotTable4</c:name>
+    <c:fmtId val="12"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="95000"/>
+                  <a:lumOff val="5000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Monthly Revenue'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Monthly Revenue'!$A$2:$A$50</c:f>
+              <c:strCache>
+                <c:ptCount val="48"/>
+                <c:pt idx="0">
+                  <c:v>2022-01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022-02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2022-03</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2022-04</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2022-05</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2022-06</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2022-07</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2022-08</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2022-09</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2022-10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2022-11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2022-12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2023-01</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2023-02</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2023-03</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2023-04</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2023-05</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2023-06</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023-07</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2023-08</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2023-09</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2023-10</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2023-11</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023-12</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024-01</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2024-02</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2024-03</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2024-04</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2024-05</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2024-06</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2024-07</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2024-08</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2024-09</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2024-10</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2024-11</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2024-12</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2025-01</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2025-02</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2025-03</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2025-04</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2025-05</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2025-06</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2025-07</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2025-08</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2025-09</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2025-10</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2025-11</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2025-12</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Monthly Revenue'!$B$2:$B$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="48"/>
+                <c:pt idx="0">
+                  <c:v>58635.53</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60262.97</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>57143.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>56880.02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>51805.22</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60549.86</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>56250.74</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>55052.53</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>60495.63</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>56896.98</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>58402.69</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>55006.46</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>85210.01</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>86906.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>79964.160000000003</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>97173.99</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>101370.73</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>83465.899999999994</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>90818.8</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>89422.22</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>89196.88</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>85095.72</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>79627.33</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>75904.66</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>94306.43</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>75083.7</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>99439.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>99105.22</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>87328.99</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>86955.71</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>89422.22</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>91189.41</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>83103.19</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>80543.34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>74988.649999999994</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>85210.01</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>135193.89000000001</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>104990.83</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>119415.67999999999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>117652.02</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>119352.07</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>135192.03</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>126976.23</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>133776.6</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>119597</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>185241.67</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>126941.06</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>128272.56</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-716C-47AA-BAC1-45B85F6C21D3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="591950463"/>
+        <c:axId val="591950943"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="591950463"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="591950943"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="591950943"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="591950463"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:legendEntry>
+        <c:idx val="1"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="101"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="1"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[worrobah_territory_chart.xlsx]Total Revenue!PivotTable6</c:name>
+    <c:fmtId val="6"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="dk1">
+              <a:tint val="88500"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:tint val="88500"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:tint val="88500"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="dk1">
+              <a:tint val="88500"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Total Revenue'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:tint val="88500"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="10"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-E49E-4117-BD17-B00718C65B8C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="11"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-E49E-4117-BD17-B00718C65B8C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Total Revenue'!$A$2:$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Queens</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oswego</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Brooklyn</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Syracuse</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Albany</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Plattsburgh</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Ithaca</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Elmira</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Buffalo</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Poestenkill</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Rochester</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>New York</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Total Revenue'!$B$2:$B$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>288553.14</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>302862.71000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>304732.76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>306998.14</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>310389.02</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>311520.52</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>313920.05</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>313971.65000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>314979.99</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>334175.88</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>607148.21</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>621565.02</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E49E-4117-BD17-B00718C65B8C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="596524735"/>
+        <c:axId val="596523775"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="596524735"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="596523775"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="596523775"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="596524735"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2503,87 +2738,40 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="16">
   <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
 </cs:colorStyle>
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="20">
+  <a:schemeClr val="dk1"/>
   <cs:variation>
-    <a:lumMod val="60000"/>
+    <a:tint val="88500"/>
   </cs:variation>
   <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
+    <a:tint val="55000"/>
   </cs:variation>
   <cs:variation>
-    <a:lumMod val="80000"/>
+    <a:tint val="75000"/>
   </cs:variation>
   <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
+    <a:tint val="98500"/>
   </cs:variation>
   <cs:variation>
-    <a:lumMod val="50000"/>
+    <a:tint val="30000"/>
   </cs:variation>
   <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
+    <a:tint val="60000"/>
   </cs:variation>
   <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
+    <a:tint val="80000"/>
   </cs:variation>
 </cs:colorStyle>
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2691,6 +2879,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -2701,6 +2894,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -2732,6 +2930,9 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3086,7 +3287,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3194,6 +3395,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -3204,6 +3410,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -3235,6 +3446,9 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3589,7 +3803,7 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3697,11 +3911,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -3712,11 +3921,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -3748,9 +3952,6 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3806,22 +4007,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -3926,8 +4128,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -4059,19 +4261,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -4105,88 +4308,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C5A8D5B-763C-E105-C53F-C7A9A2E71B6D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D459BA61-85CE-B73D-5B91-A92D6884D6C8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -4227,20 +4348,20 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>351692</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>82061</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4255,14 +4376,16 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="12830175" cy="6838950"/>
+          <a:off x="351692" y="232228"/>
+          <a:ext cx="13141569" cy="8060871"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="bg1"/>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -4294,16 +4417,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>190499</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>70757</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>52251</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>409575</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>289832</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>100149</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4318,13 +4441,17 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="190500" y="190499"/>
-          <a:ext cx="3876675" cy="1000125"/>
+          <a:off x="680357" y="422365"/>
+          <a:ext cx="3876675" cy="973184"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:ln>
           <a:solidFill>
             <a:schemeClr val="tx2">
@@ -4356,7 +4483,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1800">
+            <a:rPr lang="en-US" sz="1400">
               <a:solidFill>
                 <a:schemeClr val="tx2">
                   <a:lumMod val="90000"/>
@@ -4372,7 +4499,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="3200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2400" b="1" i="0" u="none" strike="noStrike">
               <a:ln>
                 <a:solidFill>
                   <a:schemeClr val="tx2">
@@ -4392,7 +4519,7 @@
             <a:t>4330817.09</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="3200">
+            <a:rPr lang="en-US" sz="2400">
               <a:solidFill>
                 <a:schemeClr val="tx2">
                   <a:lumMod val="50000"/>
@@ -4405,7 +4532,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="3200">
+          <a:endParaRPr lang="en-US" sz="2400">
             <a:solidFill>
               <a:schemeClr val="tx2">
                 <a:lumMod val="50000"/>
@@ -4422,16 +4549,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>343690</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>26663</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>394270</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>122514</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4460,8 +4587,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="200025" y="219075"/>
-          <a:ext cx="914400" cy="914400"/>
+          <a:off x="953290" y="581834"/>
+          <a:ext cx="660180" cy="651023"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4472,16 +4599,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>70757</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>63953</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>409575</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>57149</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>289832</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>120281</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4496,13 +4623,17 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4457700" y="200024"/>
-          <a:ext cx="3876675" cy="1000125"/>
+          <a:off x="4947557" y="434067"/>
+          <a:ext cx="3876675" cy="981614"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:ln>
           <a:solidFill>
             <a:schemeClr val="tx2">
@@ -4534,7 +4665,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1800">
+            <a:rPr lang="en-US" sz="1400">
               <a:solidFill>
                 <a:schemeClr val="tx2">
                   <a:lumMod val="90000"/>
@@ -4550,7 +4681,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="3200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2400" b="1" i="0" u="none" strike="noStrike">
               <a:ln>
                 <a:solidFill>
                   <a:schemeClr val="tx2">
@@ -4569,8 +4700,29 @@
             </a:rPr>
             <a:t>2022-01</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="3200">
+            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>Earliest Transaction</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
               <a:solidFill>
                 <a:schemeClr val="tx2">
                   <a:lumMod val="50000"/>
@@ -4583,7 +4735,10 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="3200">
+          <a:endParaRPr lang="en-US" sz="1200">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
             <a:solidFill>
               <a:schemeClr val="tx2">
                 <a:lumMod val="50000"/>
@@ -4600,16 +4755,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>190499</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>80282</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>52251</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>299357</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>100149</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4624,13 +4779,17 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8734425" y="190499"/>
-          <a:ext cx="3876675" cy="1000125"/>
+          <a:off x="9224282" y="422365"/>
+          <a:ext cx="3876675" cy="973184"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:ln>
           <a:solidFill>
             <a:schemeClr val="tx2">
@@ -4662,7 +4821,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1800">
+            <a:rPr lang="en-US" sz="1400">
               <a:solidFill>
                 <a:schemeClr val="tx2">
                   <a:lumMod val="90000"/>
@@ -4675,7 +4834,7 @@
             <a:t>End</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1800" baseline="0">
+            <a:rPr lang="en-US" sz="1400" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx2">
                   <a:lumMod val="90000"/>
@@ -4687,7 +4846,7 @@
             </a:rPr>
             <a:t> Date</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1800">
+          <a:endParaRPr lang="en-US" sz="1400">
             <a:solidFill>
               <a:schemeClr val="tx2">
                 <a:lumMod val="90000"/>
@@ -4701,7 +4860,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="3200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2400" b="1" i="0" u="none" strike="noStrike">
               <a:ln>
                 <a:solidFill>
                   <a:schemeClr val="tx2">
@@ -4720,8 +4879,44 @@
             </a:rPr>
             <a:t>2025-12</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="3200">
+            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>Latest</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t> Transaction </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
               <a:solidFill>
                 <a:schemeClr val="tx2">
                   <a:lumMod val="50000"/>
@@ -4734,7 +4929,10 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="3200">
+          <a:endParaRPr lang="en-US" sz="1200">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
             <a:solidFill>
               <a:schemeClr val="tx2">
                 <a:lumMod val="50000"/>
@@ -4749,17 +4947,1274 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>393903</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>124187</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>555710</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>163743</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Graphic 4" descr="Daily calendar with solid fill">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4A73445-27D3-F78B-2A0D-DC984A6A4047}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9537903" y="494301"/>
+          <a:ext cx="771407" cy="779785"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>455238</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>134530</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>602746</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>160168</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Graphic 5" descr="Daily calendar with solid fill">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0673CBD6-D79A-41CF-AE4D-FF3CE8E5F4D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5332038" y="504644"/>
+          <a:ext cx="757108" cy="765867"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>489857</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>129689</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>218923</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>115389</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Rectangle: Rounded Corners 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4C3BE87-FE7C-D37A-16AC-576A54F3ACE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="489857" y="1795203"/>
+          <a:ext cx="6434666" cy="4056957"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>246712</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>165269</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>115008</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>106098</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17FA8A75-9AB1-50EB-343B-86D78E9F7109}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>237738</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>93940</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>548184</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Rectangle: Rounded Corners 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F79232F4-BE05-401D-BD44-D9A9772F1162}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6943338" y="1694140"/>
+          <a:ext cx="6406446" cy="3944660"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>243759</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>114635</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>130871</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>51875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7981E06-955B-2AC3-9DAA-91F99891870A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>575310</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>88843</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>109345</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>100965</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="Straight Connector 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7ADB74B6-5042-32F9-3933-3A9754370BDC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="575310" y="2100523"/>
+          <a:ext cx="6239635" cy="12122"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>237506</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>114795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>436665</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>80158</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="TextBox 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC728951-03CF-442B-AD26-04F8191CE727}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2066306" y="1780309"/>
+          <a:ext cx="3247159" cy="335478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>MONTHLY</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t> REVENUE TREND</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1400" b="1">
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>314368</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>80694</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>464790</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>88843</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="Straight Connector 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D400A5E3-F5CA-43EA-829A-CC38D831A8BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7004933" y="2110416"/>
+          <a:ext cx="6232754" cy="8149"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>531750</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>121721</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>29754</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>87084</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="TextBox 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CC06975-8D0E-497E-A478-779DA50947CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8456550" y="1787235"/>
+          <a:ext cx="3765204" cy="335478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="1">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>Store Sales Performance (Total Revenue)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>293162</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>2903</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>374441</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>157480</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="Rectangle 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C2848C2-1FA4-4A0B-B6BE-CAB03F970B80}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="902762" y="5159103"/>
+          <a:ext cx="690879" cy="332377"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>338296</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>173278</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>117231</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>140678</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="Rectangle 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07A05361-CBA2-4BA2-96F1-1995C94DFEDB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="947896" y="2236540"/>
+          <a:ext cx="1607735" cy="342538"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>321917</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1840</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>464156</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>157215</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Rectangle 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB634963-94B9-4C53-99EF-847ED38C7A93}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7068405" y="2232084"/>
+          <a:ext cx="1368873" cy="341229"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>255718</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>103777</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>72837</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>73297</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="Rectangle 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77D1A8D4-CB99-4D49-B431-E5E99C0C881D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7002206" y="3820850"/>
+          <a:ext cx="1043753" cy="341227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>489857</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>88899</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>218923</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>155302</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="Rectangle: Rounded Corners 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5C2BB45-DFA9-48E6-8900-80C3819C4CF1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="489857" y="5778499"/>
+          <a:ext cx="6434666" cy="2377803"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>223157</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>50799</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>561823</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>117202</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="Rectangle: Rounded Corners 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2423B666-CF18-4FF5-BA41-3755B41BF783}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6928757" y="5740399"/>
+          <a:ext cx="6434666" cy="2377803"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>190501</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>7743</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4699000" cy="1566776"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="TextBox 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61CD28C0-7E2A-F26B-674D-E461A12DF159}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2019301" y="6230743"/>
+          <a:ext cx="4699000" cy="1566776"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="2000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>Revenue rises from 2022 to 2025, with the strongest spike in October 2025. New York and Rochester are the highest-performing stores and clearly lead the territory</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="2000" b="1">
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>482600</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>122041</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4845957" cy="1566776"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="TextBox 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3A50CBA-9962-4725-B600-B2199534CE37}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8407400" y="6167241"/>
+          <a:ext cx="4845957" cy="1566776"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="2000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>Focus next quarter’s sales attention on New York and Rochester. Increase inventory and marketing in those stores, then use targeted promotions to lift lower-performing locations.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="2000" b="1">
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>546100</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="Graphic 38" descr="Bullseye with solid fill">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25366ED3-99C8-59C0-1EE3-A6DE08840199}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId8"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7226300" y="6311900"/>
+          <a:ext cx="1244600" cy="1244600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>200800</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>147600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>48400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="41" name="Graphic 40" descr="Bar chart with solid fill">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0C09D97-7252-B8ED-9CB6-F35B58925FB4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId10"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="810400" y="6370600"/>
+          <a:ext cx="1145400" cy="1145400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Jordan's River" refreshedDate="46142.620591319443" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="49" xr:uid="{B429A545-8688-4429-8878-E848810C8F33}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Jordan's River" refreshedDate="46142.622127199073" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{7E204DBD-F25C-4233-9B5E-C8832F9102FF}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:B1048576" sheet="worrobah_territory_chart"/>
+    <worksheetSource ref="C1:D13" sheet="worrobah_territory_chart"/>
+  </cacheSource>
+  <cacheFields count="2">
+    <cacheField name="StoreLocation" numFmtId="0">
+      <sharedItems count="12">
+        <s v="New York"/>
+        <s v="Rochester"/>
+        <s v="Poestenkill"/>
+        <s v="Buffalo"/>
+        <s v="Elmira"/>
+        <s v="Ithaca"/>
+        <s v="Plattsburgh"/>
+        <s v="Albany"/>
+        <s v="Syracuse"/>
+        <s v="Brooklyn"/>
+        <s v="Oswego"/>
+        <s v="Queens"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Total_Revenue" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="288553.14" maxValue="621565.02"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Jordan Worrobah" refreshedDate="46143.228572106484" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{C0669422-61B1-481F-BC0E-90596622F973}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:B49" sheet="worrobah_territory_chart"/>
   </cacheSource>
   <cacheFields count="2">
     <cacheField name="Month" numFmtId="0">
-      <sharedItems containsBlank="1" count="49">
+      <sharedItems count="48">
         <s v="2022-01"/>
         <s v="2022-02"/>
         <s v="2022-03"/>
@@ -4808,45 +6263,10 @@
         <s v="2025-10"/>
         <s v="2025-11"/>
         <s v="2025-12"/>
-        <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="Monthly Revenue" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="51805.22" maxValue="185241.67"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Jordan's River" refreshedDate="46142.622127199073" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{7E204DBD-F25C-4233-9B5E-C8832F9102FF}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="C1:D13" sheet="worrobah_territory_chart"/>
-  </cacheSource>
-  <cacheFields count="2">
-    <cacheField name="StoreLocation" numFmtId="0">
-      <sharedItems count="12">
-        <s v="New York"/>
-        <s v="Rochester"/>
-        <s v="Poestenkill"/>
-        <s v="Buffalo"/>
-        <s v="Elmira"/>
-        <s v="Ithaca"/>
-        <s v="Plattsburgh"/>
-        <s v="Albany"/>
-        <s v="Syracuse"/>
-        <s v="Brooklyn"/>
-        <s v="Oswego"/>
-        <s v="Queens"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Total_Revenue" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="288553.14" maxValue="621565.02"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="51805.22" maxValue="185241.67"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -4858,7 +6278,60 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="49">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="12">
+  <r>
+    <x v="0"/>
+    <n v="621565.02"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="607148.21"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="334175.88"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="314979.99"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="313971.65000000002"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="313920.05"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="311520.52"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="310389.02"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="306998.14"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="304732.76"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="302862.71000000002"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="288553.14"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="48">
   <r>
     <x v="0"/>
     <n v="58635.53"/>
@@ -5051,72 +6524,15 @@
     <x v="47"/>
     <n v="128272.56"/>
   </r>
-  <r>
-    <x v="48"/>
-    <m/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="12">
-  <r>
-    <x v="0"/>
-    <n v="621565.02"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <n v="607148.21"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <n v="334175.88"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <n v="314979.99"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <n v="313971.65000000002"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <n v="313920.05"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <n v="311520.52"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <n v="310389.02"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <n v="306998.14"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <n v="304732.76"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <n v="302862.71000000002"/>
-  </r>
-  <r>
-    <x v="11"/>
-    <n v="288553.14"/>
-  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8F7AB9DF-AED6-4202-9FF5-4A3B175E4250}" name="PivotTable4" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
-  <location ref="A1:B51" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{995154EF-3220-4285-A91D-4F1D3924D228}" name="PivotTable4" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
+  <location ref="A1:B50" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" showAll="0">
-      <items count="50">
+      <items count="49">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -5165,7 +6581,6 @@
         <item x="45"/>
         <item x="46"/>
         <item x="47"/>
-        <item x="48"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -5174,7 +6589,7 @@
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="50">
+  <rowItems count="49">
     <i>
       <x/>
     </i>
@@ -5319,9 +6734,6 @@
     <i>
       <x v="47"/>
     </i>
-    <i>
-      <x v="48"/>
-    </i>
     <i t="grand">
       <x/>
     </i>
@@ -5333,7 +6745,7 @@
     <dataField name="Sum of Monthly Revenue" fld="1" baseField="0" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
+    <chartFormat chart="12" format="1" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5356,10 +6768,10 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{42F2BBB6-A436-4E8D-AC4A-910B90B981E1}" name="PivotTable6" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{42F2BBB6-A436-4E8D-AC4A-910B90B981E1}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="A1:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
       <items count="13">
         <item x="7"/>
         <item x="9"/>
@@ -5375,6 +6787,15 @@
         <item x="8"/>
         <item t="default"/>
       </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
     </pivotField>
     <pivotField dataField="1" showAll="0"/>
   </pivotFields>
@@ -5383,40 +6804,40 @@
   </rowFields>
   <rowItems count="13">
     <i>
-      <x/>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="6"/>
     </i>
     <i>
       <x v="1"/>
     </i>
     <i>
-      <x v="2"/>
+      <x v="11"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="4"/>
     </i>
     <i>
       <x v="3"/>
     </i>
     <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
+      <x v="2"/>
     </i>
     <i>
       <x v="8"/>
     </i>
     <i>
-      <x v="9"/>
-    </i>
-    <i>
       <x v="10"/>
     </i>
     <i>
-      <x v="11"/>
+      <x v="5"/>
     </i>
     <i t="grand">
       <x/>
@@ -5428,12 +6849,36 @@
   <dataFields count="1">
     <dataField name="Sum of Total_Revenue" fld="1" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
+  <chartFormats count="3">
+    <chartFormat chart="6" format="1" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="10"/>
           </reference>
         </references>
       </pivotArea>
@@ -5454,7 +6899,7 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Aspect">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5462,34 +6907,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="323232"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E3DED1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="F07F09"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="9F2936"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="1B587C"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="4E8542"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="604878"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="C19859"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="6B9F25"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="B26B02"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -5768,22 +7213,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23B901C8-2ED8-4BE2-8E1E-B68F66D1E0C7}">
-  <dimension ref="A1:B51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -5791,7 +7236,7 @@
         <v>58635.53</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -5799,7 +7244,7 @@
         <v>60262.97</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -5807,7 +7252,7 @@
         <v>57143.4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -5815,7 +7260,7 @@
         <v>56880.02</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -5823,7 +7268,7 @@
         <v>51805.22</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -5831,7 +7276,7 @@
         <v>60549.86</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
@@ -5839,7 +7284,7 @@
         <v>56250.74</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
@@ -5847,7 +7292,7 @@
         <v>55052.53</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -5855,7 +7300,7 @@
         <v>60495.63</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
@@ -5863,7 +7308,7 @@
         <v>56896.98</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
@@ -5871,7 +7316,7 @@
         <v>58402.69</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
@@ -5879,7 +7324,7 @@
         <v>55006.46</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
@@ -5887,7 +7332,7 @@
         <v>85210.01</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
@@ -5895,7 +7340,7 @@
         <v>86906.65</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
@@ -5903,7 +7348,7 @@
         <v>79964.160000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
@@ -5911,7 +7356,7 @@
         <v>97173.99</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
@@ -5919,7 +7364,7 @@
         <v>101370.73</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
@@ -5927,7 +7372,7 @@
         <v>83465.899999999994</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
@@ -5935,7 +7380,7 @@
         <v>90818.8</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
@@ -5943,7 +7388,7 @@
         <v>89422.22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
@@ -5951,7 +7396,7 @@
         <v>89196.88</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>23</v>
       </c>
@@ -5959,7 +7404,7 @@
         <v>85095.72</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
@@ -5967,7 +7412,7 @@
         <v>79627.33</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>25</v>
       </c>
@@ -5975,7 +7420,7 @@
         <v>75904.66</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
@@ -5983,7 +7428,7 @@
         <v>94306.43</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
@@ -5991,7 +7436,7 @@
         <v>75083.7</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
@@ -5999,7 +7444,7 @@
         <v>99439.5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>29</v>
       </c>
@@ -6007,7 +7452,7 @@
         <v>99105.22</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>30</v>
       </c>
@@ -6015,7 +7460,7 @@
         <v>87328.99</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>31</v>
       </c>
@@ -6023,7 +7468,7 @@
         <v>86955.71</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -6031,7 +7476,7 @@
         <v>89422.22</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>33</v>
       </c>
@@ -6039,7 +7484,7 @@
         <v>91189.41</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>34</v>
       </c>
@@ -6047,7 +7492,7 @@
         <v>83103.19</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>35</v>
       </c>
@@ -6055,7 +7500,7 @@
         <v>80543.34</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>36</v>
       </c>
@@ -6063,7 +7508,7 @@
         <v>74988.649999999994</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>37</v>
       </c>
@@ -6071,7 +7516,7 @@
         <v>85210.01</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>38</v>
       </c>
@@ -6079,7 +7524,7 @@
         <v>135193.89000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>39</v>
       </c>
@@ -6087,7 +7532,7 @@
         <v>104990.83</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>40</v>
       </c>
@@ -6095,7 +7540,7 @@
         <v>119415.67999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>41</v>
       </c>
@@ -6103,7 +7548,7 @@
         <v>117652.02</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>42</v>
       </c>
@@ -6111,7 +7556,7 @@
         <v>119352.07</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>43</v>
       </c>
@@ -6119,7 +7564,7 @@
         <v>135192.03</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>44</v>
       </c>
@@ -6127,7 +7572,7 @@
         <v>126976.23</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>45</v>
       </c>
@@ -6135,7 +7580,7 @@
         <v>133776.6</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>46</v>
       </c>
@@ -6143,7 +7588,7 @@
         <v>119597</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>47</v>
       </c>
@@ -6151,7 +7596,7 @@
         <v>185241.67</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>48</v>
       </c>
@@ -6159,7 +7604,7 @@
         <v>126941.06</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>49</v>
       </c>
@@ -6167,124 +7612,117 @@
         <v>128272.56</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B50" s="3"/>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B51" s="3">
+      <c r="B50" s="3">
         <v>4330817.09</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC3FA750-5E0E-4779-A265-AF02A75A3C9E}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="3">
+        <v>288553.14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="3">
+        <v>302862.71000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="3">
+        <v>304732.76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="3">
+        <v>306998.14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B6" s="3">
         <v>310389.02</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="3">
-        <v>304732.76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="3">
+        <v>311520.52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="3">
+        <v>313920.05</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="3">
+        <v>313971.65000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B10" s="3">
         <v>314979.99</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="3">
-        <v>313971.65000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="3">
-        <v>313920.05</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="3">
-        <v>621565.02</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="3">
-        <v>302862.71000000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="3">
-        <v>311520.52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B11" s="3">
         <v>334175.88</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" s="3">
-        <v>288553.14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>53</v>
       </c>
@@ -6292,17 +7730,17 @@
         <v>607148.21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B13" s="3">
-        <v>306998.14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>621565.02</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B14" s="3">
         <v>4330817.09</v>
@@ -6310,16 +7748,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2AE86FD-AE2F-4F2D-B94C-1294817694AF}">
   <dimension ref="A1:D49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6333,7 +7770,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6347,7 +7784,7 @@
         <v>621565.02</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -6361,7 +7798,7 @@
         <v>607148.21</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -6375,7 +7812,7 @@
         <v>334175.88</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -6389,7 +7826,7 @@
         <v>314979.99</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -6403,7 +7840,7 @@
         <v>313971.65000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -6417,7 +7854,7 @@
         <v>313920.05</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -6431,7 +7868,7 @@
         <v>311520.52</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -6445,7 +7882,7 @@
         <v>310389.02</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -6459,7 +7896,7 @@
         <v>306998.14</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -6473,7 +7910,7 @@
         <v>304732.76</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -6487,7 +7924,7 @@
         <v>302862.71000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -6501,7 +7938,7 @@
         <v>288553.14</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -6509,7 +7946,7 @@
         <v>85210.01</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -6517,7 +7954,7 @@
         <v>86906.65</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -6525,7 +7962,7 @@
         <v>79964.160000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -6533,7 +7970,7 @@
         <v>97173.99</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -6541,7 +7978,7 @@
         <v>101370.73</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -6549,7 +7986,7 @@
         <v>83465.899999999994</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -6557,7 +7994,7 @@
         <v>90818.8</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -6565,7 +8002,7 @@
         <v>89422.22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -6573,7 +8010,7 @@
         <v>89196.88</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -6581,7 +8018,7 @@
         <v>85095.72</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -6589,7 +8026,7 @@
         <v>79627.33</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -6597,7 +8034,7 @@
         <v>75904.66</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -6605,7 +8042,7 @@
         <v>94306.43</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -6613,7 +8050,7 @@
         <v>75083.7</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -6621,7 +8058,7 @@
         <v>99439.5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -6629,7 +8066,7 @@
         <v>99105.22</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -6637,7 +8074,7 @@
         <v>87328.99</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -6645,7 +8082,7 @@
         <v>86955.71</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -6653,7 +8090,7 @@
         <v>89422.22</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -6661,7 +8098,7 @@
         <v>91189.41</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -6669,7 +8106,7 @@
         <v>83103.19</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -6677,7 +8114,7 @@
         <v>80543.34</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -6685,7 +8122,7 @@
         <v>74988.649999999994</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -6693,7 +8130,7 @@
         <v>85210.01</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -6701,7 +8138,7 @@
         <v>135193.89000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -6709,7 +8146,7 @@
         <v>104990.83</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -6717,7 +8154,7 @@
         <v>119415.67999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -6725,7 +8162,7 @@
         <v>117652.02</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -6733,7 +8170,7 @@
         <v>119352.07</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -6741,7 +8178,7 @@
         <v>135192.03</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -6749,7 +8186,7 @@
         <v>126976.23</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -6757,7 +8194,7 @@
         <v>133776.6</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>46</v>
       </c>
@@ -6765,7 +8202,7 @@
         <v>119597</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -6773,7 +8210,7 @@
         <v>185241.67</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -6781,7 +8218,7 @@
         <v>126941.06</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -6798,7 +8235,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8DFECF4-AE29-4D9C-9BB1-A35C803973CA}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
